--- a/testakten/startup-gruender-schnittflug-berlin/52_Mehrheiten_und_Bezugsrechte.xlsx
+++ b/testakten/startup-gruender-schnittflug-berlin/52_Mehrheiten_und_Bezugsrechte.xlsx
@@ -2,14 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abstimmung" sheetId="1" r:id="Rdecdac363e1148a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bezugsrechte" sheetId="2" r:id="Red0b5fafc7d44b99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eingaben" sheetId="3" r:id="R85e061d6c82349aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abstimmung" sheetId="1" r:id="Rbc2071d28eb645c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bezugsrechte" sheetId="2" r:id="Rf13e4e1d8fef45a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eingaben" sheetId="3" r:id="R6f5657b32db64fd5"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Abstimmung'!$B$2:$G$36</x:definedName>
+    <x:definedName name="_xlnm.Print_Titles" localSheetId="0">'Abstimmung'!$2:$5</x:definedName>
     <x:definedName name="_xlnm.Print_Area" localSheetId="1">'Bezugsrechte'!$B$2:$I$34</x:definedName>
+    <x:definedName name="_xlnm.Print_Titles" localSheetId="1">'Bezugsrechte'!$13:$13</x:definedName>
     <x:definedName name="_xlnm.Print_Area" localSheetId="2">'Eingaben'!$B$2:$G$37</x:definedName>
+    <x:definedName name="_xlnm.Print_Titles" localSheetId="2">'Eingaben'!$21:$21</x:definedName>
   </x:definedNames>
 </x:workbook>
 </file>
@@ -127,7 +130,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="56">
+  <x:cellXfs count="58">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -223,6 +226,9 @@
     <x:xf numFmtId="200" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -246,6 +252,9 @@
     </x:xf>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -604,7 +613,7 @@
         <x:f>'Eingaben'!C7</x:f>
         <x:v>5250</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="str">
+      <x:c r="D8" s="33" t="str">
         <x:f>INDEX('Eingaben'!$C$22:$G$28,1,$C$5)</x:f>
         <x:v>Nein</x:v>
       </x:c>
@@ -626,7 +635,7 @@
         <x:f>'Eingaben'!C8</x:f>
         <x:v>5500</x:v>
       </x:c>
-      <x:c r="D9" s="30" t="str">
+      <x:c r="D9" s="33" t="str">
         <x:f>INDEX('Eingaben'!$C$22:$G$28,2,$C$5)</x:f>
         <x:v>Ja</x:v>
       </x:c>
@@ -648,7 +657,7 @@
         <x:f>'Eingaben'!C9</x:f>
         <x:v>4500</x:v>
       </x:c>
-      <x:c r="D10" s="30" t="str">
+      <x:c r="D10" s="33" t="str">
         <x:f>INDEX('Eingaben'!$C$22:$G$28,3,$C$5)</x:f>
         <x:v>Ja</x:v>
       </x:c>
@@ -670,7 +679,7 @@
         <x:f>'Eingaben'!C10</x:f>
         <x:v>3750</x:v>
       </x:c>
-      <x:c r="D11" s="30" t="str">
+      <x:c r="D11" s="33" t="str">
         <x:f>INDEX('Eingaben'!$C$22:$G$28,4,$C$5)</x:f>
         <x:v>Ja</x:v>
       </x:c>
@@ -692,7 +701,7 @@
         <x:f>'Eingaben'!C11</x:f>
         <x:v>2500</x:v>
       </x:c>
-      <x:c r="D12" s="30" t="str">
+      <x:c r="D12" s="33" t="str">
         <x:f>INDEX('Eingaben'!$C$22:$G$28,5,$C$5)</x:f>
         <x:v>Ja</x:v>
       </x:c>
@@ -714,7 +723,7 @@
         <x:f>'Eingaben'!C12</x:f>
         <x:v>2000</x:v>
       </x:c>
-      <x:c r="D13" s="30" t="str">
+      <x:c r="D13" s="33" t="str">
         <x:f>INDEX('Eingaben'!$C$22:$G$28,6,$C$5)</x:f>
         <x:v>Ja</x:v>
       </x:c>
@@ -736,7 +745,7 @@
         <x:f>'Eingaben'!C13</x:f>
         <x:v>1500</x:v>
       </x:c>
-      <x:c r="D14" s="30" t="str">
+      <x:c r="D14" s="33" t="str">
         <x:f>INDEX('Eingaben'!$C$22:$G$28,7,$C$5)</x:f>
         <x:v>Ja</x:v>
       </x:c>
@@ -869,11 +878,11 @@
       <x:c r="B24" s="2" t="str">
         <x:v>Ja-Anteil am jeweiligen Nenner</x:v>
       </x:c>
-      <x:c r="C24" s="34" t="n">
+      <x:c r="C24" s="35" t="n">
         <x:f>IF(C19=0,"n.a.",C17/C19)</x:f>
         <x:v>0.79</x:v>
       </x:c>
-      <x:c r="D24" s="34" t="n">
+      <x:c r="D24" s="35" t="n">
         <x:f>C17/C20</x:f>
         <x:v>0.79</x:v>
       </x:c>
@@ -887,11 +896,11 @@
       <x:c r="B25" s="2" t="str">
         <x:v>Erforderliche Quote</x:v>
       </x:c>
-      <x:c r="C25" s="36" t="n">
+      <x:c r="C25" s="37" t="n">
         <x:f>'Eingaben'!C18</x:f>
         <x:v>0.75</x:v>
       </x:c>
-      <x:c r="D25" s="34" t="n">
+      <x:c r="D25" s="35" t="n">
         <x:f>C25</x:f>
         <x:v>0.75</x:v>
       </x:c>
@@ -905,11 +914,11 @@
       <x:c r="B26" s="2" t="str">
         <x:v>Quote rechnerisch erreicht?</x:v>
       </x:c>
-      <x:c r="C26" s="37" t="str">
+      <x:c r="C26" s="38" t="str">
         <x:f>IF(C19=0,"Keine gültige Stimme",IF(C24&gt;=C25,"Ja","Nein"))</x:f>
         <x:v>Ja</x:v>
       </x:c>
-      <x:c r="D26" s="37" t="str">
+      <x:c r="D26" s="38" t="str">
         <x:f>IF(D24&gt;=D25,"Ja","Nein")</x:f>
         <x:v>Ja</x:v>
       </x:c>
@@ -943,7 +952,7 @@
       <x:c r="B29" s="2" t="str">
         <x:v>Ottilies Kapitalanteil bei Gründung</x:v>
       </x:c>
-      <x:c r="C29" s="36" t="n">
+      <x:c r="C29" s="37" t="n">
         <x:f>'Eingaben'!C7/'Eingaben'!C15</x:f>
         <x:v>0.21</x:v>
       </x:c>
@@ -1073,6 +1082,9 @@
   </x:dataValidations>
   <x:pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <x:rowBreaks count="1" manualBreakCount="1">
+    <x:brk id="22" min="0" max="16383" man="1"/>
+  </x:rowBreaks>
 </x:worksheet>
 </file>
 
@@ -1087,7 +1099,7 @@
     <x:col min="1" max="1" width="2" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="43.33000183105469" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="16.110000610351562" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20.559999465942383" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="16.110000610351562" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="16.110000610351562" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="17.219999313354492" hidden="0" customWidth="1"/>
@@ -1178,7 +1190,7 @@
         <x:f>SUM('Eingaben'!C7:C13)+C9+C10</x:f>
         <x:v>40000</x:v>
       </x:c>
-      <x:c r="D7" s="2" t="str">
+      <x:c r="D7" s="42" t="str">
         <x:v>Neu nominal EUR</x:v>
       </x:c>
       <x:c r="E7" s="15" t="n">
@@ -1194,13 +1206,13 @@
       <x:c r="B8" s="2" t="str">
         <x:v>Zufluss Serie B (EUR)</x:v>
       </x:c>
-      <x:c r="C8" s="38" t="n">
+      <x:c r="C8" s="39" t="n">
         <x:v>1800000</x:v>
       </x:c>
-      <x:c r="D8" s="2" t="str">
+      <x:c r="D8" s="42" t="str">
         <x:v>Preis / EUR nominal</x:v>
       </x:c>
-      <x:c r="E8" s="40" t="n">
+      <x:c r="E8" s="41" t="n">
         <x:f>C8/E7</x:f>
         <x:v>90</x:v>
       </x:c>
@@ -1297,7 +1309,7 @@
         <x:f>'Eingaben'!C7</x:f>
         <x:v>5250</x:v>
       </x:c>
-      <x:c r="D14" s="45" t="n">
+      <x:c r="D14" s="47" t="n">
         <x:f>C14/$C$7*$E$7</x:f>
         <x:v>2625</x:v>
       </x:c>
@@ -1305,7 +1317,7 @@
         <x:f>IF($C$5=1,ROUNDDOWN(D14,0),IF(AND($C$5=3,1=1),ROUNDDOWN(D14,0),0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" s="45" t="n">
+      <x:c r="F14" s="47" t="n">
         <x:f>IF($C$5=1,D14-E14,IF(AND($C$5=3,1=1),D14-E14,0))</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1313,11 +1325,11 @@
         <x:f>SUM(C14,E14)</x:f>
         <x:v>5250</x:v>
       </x:c>
-      <x:c r="H14" s="34" t="n">
+      <x:c r="H14" s="35" t="n">
         <x:f>G14/($C$7+$E$7)</x:f>
         <x:v>0.0875</x:v>
       </x:c>
-      <x:c r="I14" s="40" t="n">
+      <x:c r="I14" s="41" t="n">
         <x:f>E14*$E$8</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1331,7 +1343,7 @@
         <x:f>'Eingaben'!C8</x:f>
         <x:v>5500</x:v>
       </x:c>
-      <x:c r="D15" s="45" t="n">
+      <x:c r="D15" s="47" t="n">
         <x:f>C15/$C$7*$E$7</x:f>
         <x:v>2750</x:v>
       </x:c>
@@ -1339,7 +1351,7 @@
         <x:f>IF($C$5=1,ROUNDDOWN(D15,0),IF(AND($C$5=3,2=1),ROUNDDOWN(D15,0),0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F15" s="45" t="n">
+      <x:c r="F15" s="47" t="n">
         <x:f>IF($C$5=1,D15-E15,IF(AND($C$5=3,2=1),D15-E15,0))</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1347,11 +1359,11 @@
         <x:f>SUM(C15,E15)</x:f>
         <x:v>5500</x:v>
       </x:c>
-      <x:c r="H15" s="34" t="n">
+      <x:c r="H15" s="35" t="n">
         <x:f>G15/($C$7+$E$7)</x:f>
         <x:v>0.09166666666666666</x:v>
       </x:c>
-      <x:c r="I15" s="40" t="n">
+      <x:c r="I15" s="41" t="n">
         <x:f>E15*$E$8</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1365,7 +1377,7 @@
         <x:f>'Eingaben'!C9</x:f>
         <x:v>4500</x:v>
       </x:c>
-      <x:c r="D16" s="45" t="n">
+      <x:c r="D16" s="47" t="n">
         <x:f>C16/$C$7*$E$7</x:f>
         <x:v>2250</x:v>
       </x:c>
@@ -1373,7 +1385,7 @@
         <x:f>IF($C$5=1,ROUNDDOWN(D16,0),IF(AND($C$5=3,3=1),ROUNDDOWN(D16,0),0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F16" s="45" t="n">
+      <x:c r="F16" s="47" t="n">
         <x:f>IF($C$5=1,D16-E16,IF(AND($C$5=3,3=1),D16-E16,0))</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1381,11 +1393,11 @@
         <x:f>SUM(C16,E16)</x:f>
         <x:v>4500</x:v>
       </x:c>
-      <x:c r="H16" s="34" t="n">
+      <x:c r="H16" s="35" t="n">
         <x:f>G16/($C$7+$E$7)</x:f>
         <x:v>0.075</x:v>
       </x:c>
-      <x:c r="I16" s="40" t="n">
+      <x:c r="I16" s="41" t="n">
         <x:f>E16*$E$8</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1399,7 +1411,7 @@
         <x:f>'Eingaben'!C10</x:f>
         <x:v>3750</x:v>
       </x:c>
-      <x:c r="D17" s="45" t="n">
+      <x:c r="D17" s="47" t="n">
         <x:f>C17/$C$7*$E$7</x:f>
         <x:v>1875</x:v>
       </x:c>
@@ -1407,7 +1419,7 @@
         <x:f>IF($C$5=1,ROUNDDOWN(D17,0),IF(AND($C$5=3,4=1),ROUNDDOWN(D17,0),0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F17" s="45" t="n">
+      <x:c r="F17" s="47" t="n">
         <x:f>IF($C$5=1,D17-E17,IF(AND($C$5=3,4=1),D17-E17,0))</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1415,11 +1427,11 @@
         <x:f>SUM(C17,E17)</x:f>
         <x:v>3750</x:v>
       </x:c>
-      <x:c r="H17" s="34" t="n">
+      <x:c r="H17" s="35" t="n">
         <x:f>G17/($C$7+$E$7)</x:f>
         <x:v>0.0625</x:v>
       </x:c>
-      <x:c r="I17" s="40" t="n">
+      <x:c r="I17" s="41" t="n">
         <x:f>E17*$E$8</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1433,7 +1445,7 @@
         <x:f>'Eingaben'!C11</x:f>
         <x:v>2500</x:v>
       </x:c>
-      <x:c r="D18" s="45" t="n">
+      <x:c r="D18" s="47" t="n">
         <x:f>C18/$C$7*$E$7</x:f>
         <x:v>1250</x:v>
       </x:c>
@@ -1441,7 +1453,7 @@
         <x:f>IF($C$5=1,ROUNDDOWN(D18,0),IF(AND($C$5=3,5=1),ROUNDDOWN(D18,0),0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="45" t="n">
+      <x:c r="F18" s="47" t="n">
         <x:f>IF($C$5=1,D18-E18,IF(AND($C$5=3,5=1),D18-E18,0))</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1449,11 +1461,11 @@
         <x:f>SUM(C18,E18)</x:f>
         <x:v>2500</x:v>
       </x:c>
-      <x:c r="H18" s="34" t="n">
+      <x:c r="H18" s="35" t="n">
         <x:f>G18/($C$7+$E$7)</x:f>
         <x:v>0.041666666666666664</x:v>
       </x:c>
-      <x:c r="I18" s="40" t="n">
+      <x:c r="I18" s="41" t="n">
         <x:f>E18*$E$8</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1467,7 +1479,7 @@
         <x:f>'Eingaben'!C12</x:f>
         <x:v>2000</x:v>
       </x:c>
-      <x:c r="D19" s="45" t="n">
+      <x:c r="D19" s="47" t="n">
         <x:f>C19/$C$7*$E$7</x:f>
         <x:v>1000</x:v>
       </x:c>
@@ -1475,7 +1487,7 @@
         <x:f>IF($C$5=1,ROUNDDOWN(D19,0),IF(AND($C$5=3,6=1),ROUNDDOWN(D19,0),0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F19" s="45" t="n">
+      <x:c r="F19" s="47" t="n">
         <x:f>IF($C$5=1,D19-E19,IF(AND($C$5=3,6=1),D19-E19,0))</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1483,11 +1495,11 @@
         <x:f>SUM(C19,E19)</x:f>
         <x:v>2000</x:v>
       </x:c>
-      <x:c r="H19" s="34" t="n">
+      <x:c r="H19" s="35" t="n">
         <x:f>G19/($C$7+$E$7)</x:f>
         <x:v>0.03333333333333333</x:v>
       </x:c>
-      <x:c r="I19" s="40" t="n">
+      <x:c r="I19" s="41" t="n">
         <x:f>E19*$E$8</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1501,7 +1513,7 @@
         <x:f>'Eingaben'!C13</x:f>
         <x:v>1500</x:v>
       </x:c>
-      <x:c r="D20" s="45" t="n">
+      <x:c r="D20" s="47" t="n">
         <x:f>C20/$C$7*$E$7</x:f>
         <x:v>750</x:v>
       </x:c>
@@ -1509,7 +1521,7 @@
         <x:f>IF($C$5=1,ROUNDDOWN(D20,0),IF(AND($C$5=3,7=1),ROUNDDOWN(D20,0),0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F20" s="45" t="n">
+      <x:c r="F20" s="47" t="n">
         <x:f>IF($C$5=1,D20-E20,IF(AND($C$5=3,7=1),D20-E20,0))</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1517,11 +1529,11 @@
         <x:f>SUM(C20,E20)</x:f>
         <x:v>1500</x:v>
       </x:c>
-      <x:c r="H20" s="34" t="n">
+      <x:c r="H20" s="35" t="n">
         <x:f>G20/($C$7+$E$7)</x:f>
         <x:v>0.025</x:v>
       </x:c>
-      <x:c r="I20" s="40" t="n">
+      <x:c r="I20" s="41" t="n">
         <x:f>E20*$E$8</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1535,7 +1547,7 @@
         <x:f>$C$9</x:f>
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="D21" s="45" t="n">
+      <x:c r="D21" s="47" t="n">
         <x:f>C21/$C$7*$E$7</x:f>
         <x:v>2500</x:v>
       </x:c>
@@ -1543,7 +1555,7 @@
         <x:f>IF($C$5=1,ROUNDDOWN(D21,0),IF(AND($C$5=3,8=1),ROUNDDOWN(D21,0),0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F21" s="45" t="n">
+      <x:c r="F21" s="47" t="n">
         <x:f>IF($C$5=1,D21-E21,IF(AND($C$5=3,8=1),D21-E21,0))</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1551,11 +1563,11 @@
         <x:f>SUM(C21,E21)</x:f>
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="H21" s="34" t="n">
+      <x:c r="H21" s="35" t="n">
         <x:f>G21/($C$7+$E$7)</x:f>
         <x:v>0.08333333333333333</x:v>
       </x:c>
-      <x:c r="I21" s="40" t="n">
+      <x:c r="I21" s="41" t="n">
         <x:f>E21*$E$8</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1569,7 +1581,7 @@
         <x:f>$C$10</x:f>
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="D22" s="45" t="n">
+      <x:c r="D22" s="47" t="n">
         <x:f>C22/$C$7*$E$7</x:f>
         <x:v>5000</x:v>
       </x:c>
@@ -1577,7 +1589,7 @@
         <x:f>IF($C$5=1,ROUNDDOWN(D22,0),IF(AND($C$5=3,9=1),ROUNDDOWN(D22,0),0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F22" s="45" t="n">
+      <x:c r="F22" s="47" t="n">
         <x:f>IF($C$5=1,D22-E22,IF(AND($C$5=3,9=1),D22-E22,0))</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1585,11 +1597,11 @@
         <x:f>SUM(C22,E22)</x:f>
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="H22" s="34" t="n">
+      <x:c r="H22" s="35" t="n">
         <x:f>G22/($C$7+$E$7)</x:f>
         <x:v>0.16666666666666666</x:v>
       </x:c>
-      <x:c r="I22" s="40" t="n">
+      <x:c r="I22" s="41" t="n">
         <x:f>E22*$E$8</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1599,28 +1611,28 @@
       <x:c r="B23" s="29" t="str">
         <x:v>Scherenwolke Growth Fund GmbH &amp; Co. KG</x:v>
       </x:c>
-      <x:c r="C23" s="44" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D23" s="46" t="n">
+      <x:c r="C23" s="46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D23" s="48" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E23" s="18" t="n">
         <x:f>$E$7-SUM(E14:E22)</x:f>
         <x:v>20000</x:v>
       </x:c>
-      <x:c r="F23" s="46" t="n">
+      <x:c r="F23" s="48" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G23" s="18" t="n">
         <x:f>SUM(C23,E23)</x:f>
         <x:v>20000</x:v>
       </x:c>
-      <x:c r="H23" s="34" t="n">
+      <x:c r="H23" s="35" t="n">
         <x:f>G23/($C$7+$E$7)</x:f>
         <x:v>0.3333333333333333</x:v>
       </x:c>
-      <x:c r="I23" s="40" t="n">
+      <x:c r="I23" s="41" t="n">
         <x:f>E23*$E$8</x:f>
         <x:v>1800000</x:v>
       </x:c>
@@ -1628,13 +1640,13 @@
     <x:row r="24" ht="25" customHeight="1">
       <x:c r="A24" s="2"/>
       <x:c r="B24" s="2"/>
-      <x:c r="C24" s="44"/>
-      <x:c r="D24" s="46"/>
-      <x:c r="E24" s="44"/>
-      <x:c r="F24" s="46"/>
-      <x:c r="G24" s="44"/>
-      <x:c r="H24" s="50"/>
-      <x:c r="I24" s="54"/>
+      <x:c r="C24" s="46"/>
+      <x:c r="D24" s="48"/>
+      <x:c r="E24" s="46"/>
+      <x:c r="F24" s="48"/>
+      <x:c r="G24" s="46"/>
+      <x:c r="H24" s="52"/>
+      <x:c r="I24" s="56"/>
     </x:row>
     <x:row r="25" ht="28" customHeight="1">
       <x:c r="A25" s="2"/>
@@ -1645,7 +1657,7 @@
         <x:f>SUM(C14:C23)</x:f>
         <x:v>40000</x:v>
       </x:c>
-      <x:c r="D25" s="47" t="n">
+      <x:c r="D25" s="49" t="n">
         <x:f>SUM(D14:D23)</x:f>
         <x:v>20000</x:v>
       </x:c>
@@ -1653,7 +1665,7 @@
         <x:f>SUM(E14:E23)</x:f>
         <x:v>20000</x:v>
       </x:c>
-      <x:c r="F25" s="47" t="n">
+      <x:c r="F25" s="49" t="n">
         <x:f>SUM(F14:F23)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1661,11 +1673,11 @@
         <x:f>SUM(G14:G23)</x:f>
         <x:v>60000</x:v>
       </x:c>
-      <x:c r="H25" s="51" t="n">
+      <x:c r="H25" s="53" t="n">
         <x:f>SUM(H14:H23)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I25" s="55" t="n">
+      <x:c r="I25" s="57" t="n">
         <x:f>SUM(I14:I23)</x:f>
         <x:v>1800000</x:v>
       </x:c>
@@ -2428,5 +2440,8 @@
   </x:dataValidations>
   <x:pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <x:rowBreaks count="1" manualBreakCount="1">
+    <x:brk id="20" min="0" max="16383" man="1"/>
+  </x:rowBreaks>
 </x:worksheet>
 </file>